--- a/YouTube이슈분석_개인채널_2026-08-07.xlsx
+++ b/YouTube이슈분석_개인채널_2026-08-07.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="78">
   <si>
     <t>날짜</t>
   </si>
@@ -95,10 +95,10 @@
     <t>-</t>
   </si>
   <si>
-    <t>미국에서 경찰의 바디캠 기록을 바탕으로 실제 사건을 재구성한 영상입니다. 차 안에 방치된 신생아가 발견된 긴박한 상황과 이후 현장에 나타난 중국인 남성의 행동을 중심으로, 현장 경찰의 대처 과정과 법 집행 절차를 교육 목적으로 다루고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 범죄 사건을 소재로 호기심을 유발하는 클릭베이트 형식의 콘텐츠이므로 객관적인 사실 확인과 과도한 몰입에 주의해야 합니다.</t>
+    <t>본 영상은 미국에서 차 안에 방치된 신생아가 발견된 실제 사건을 경찰 바디캠 영상을 통해 재구성한 것입니다. 현장에 출동한 경찰이 아이를 구조하는 과정과 이후 뒤늦게 나타난 보호자의 상황을 다루며, 긴박한 구조 현장과 법 집행 과정을 교육적 목적으로 생생하게 전달합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 썸네일과 제목을 사용한 범죄 실화 재구성 콘텐츠이므로 실제 사건의 구체적인 내막은 경찰 공식 발표를 확인하는 것이 정확합니다.</t>
   </si>
   <si>
     <t>▶</t>
@@ -119,28 +119,10 @@
     <t>17:29</t>
   </si>
   <si>
-    <t>초음속 여객기 콩코드는 속도만을 추구하며 대서양 횡단 시간을 획기적으로 단축한 항공 역사상의 혁신이었습니다. 본 영상은 콩코드의 화려한 등장부터 기술적 성취, 그리고 역사 속에 사라지기까지의 비극적인 사건과 사고들을 깊이 있게 조명하며 항공 공학의 정점과 그 이면의 한계를 되짚어봅니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 미스터리 연출이 포함되어 있으므로, 역사적 사실 확인을 위해 공식적인 항공 사고 조사 보고서를 함께 참고하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>【衝撃の結末と事件の全貌】京都南丹市小5男児事件</t>
-  </si>
-  <si>
-    <t>話題の事件</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>본 영상은 교토 난탄시에서 발생한 초등학교 5학년 남학생 실종 및 사망 사건의 전말을 다룹니다. 혈연관계가 없는 계부와의 복잡한 가정 환경 속에서 왜 어린 소년이 비극적인 희생양이 되었는지 그 배경과 사건의 충격적인 결말을 분석하며, 유사한 범죄의 재발 방지 및 경각심 고취를 목적으로 제작되었습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 썸네일과 제목으로 시선을 끄는 전형적인 사건 사고 채널이므로, 정보 습득 시 객관적인 보도 자료와 비교하며 시청하는 것이 좋습니다.</t>
+    <t>초음속 여객기 '콩코드'는 압도적인 속도로 하늘을 누비며 인류의 꿈을 실현했으나, 고비용과 안전 문제, 2000년 파리 추락 사고 등을 겪으며 결국 역사의 뒤안길로 사라졌습니다. 이 영상은 콩코드의 화려한 등장부터 비극적인 퇴장까지의 과정을 다룹니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 제목의 '시간 여행'은 실제 물리적 시간 여행이 아니라, 초음속 비행으로 인해 상대적으로 빠르게 목적지에 도착하는 체감 효과를 의미하는 자극적인 표현입니다.</t>
   </si>
   <si>
     <t>【辺野古沖転覆事件】学校の機能不全…第三者報告書が認定した重大な安全配慮義務違反【かなえ先生の切り抜き】元配信2026/08/03</t>
@@ -155,51 +137,30 @@
     <t>16:42</t>
   </si>
   <si>
-    <t>본 영상은 헤노코 앞바다에서 발생한 선박 전복 사건에 대한 제3자 조사 보고서를 바탕으로 학교 측의 심각한 안전 배려 의무 위반과 부적절한 인솔 과정을 분석합니다. 사건 전날부터 당일까지 교사들의 무책임한 대응과 기능 부전 상태를 비판하며, 교육 현장의 안전 관리에 대한 경종을 울리고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 사건사고를 다루는 분석 영상이므로, 객관적인 팩트와 주관적인 해석을 구분하여 시청하는 것이 중요합니다.</t>
+    <t>본 영상은 헤노코 앞바다에서 발생한 선박 전복 사건에 대해 제3자 조사위원회의 보고서를 분석합니다. 학교 측의 심각한 안전 배려 의무 위반과 사건 당일 인솔 교사들의 무책임한 대응 및 기능 부전을 다루며, 사고 전날부터 당일까지의 경과를 상세히 짚어 교육 기관의 안전 관리 체계의 문제점을 비판적으로 고찰합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 소재를 다루고 있으므로 감정적인 동요를 주의하며 공적인 보고서 내용 중심의 사실 관계 파악에 집중하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>【自動車解説】最強の高性能エンジン！実は全部ウソでした・・・【ディーゼルゲート】【フォルクスワーゲン TDI エンジン】</t>
+  </si>
+  <si>
+    <t>Winston-GAMES</t>
+  </si>
+  <si>
+    <t>14:58</t>
+  </si>
+  <si>
+    <t>본 영상은 폭스바겐의 디젤게이트 사건을 다룹니다. 당시 친환경 고성능 엔진으로 주목받던 TDI 엔진이 사실은 배기가스 저감 장치를 조작하여 환경 기준을 통과했다는 충격적인 부정행위가 밝혀진 과정을 설명합니다. 이 사건이 자동차 산업에 끼친 영향과 이후의 변화를 상세히 분석합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 썸네일과 제목을 사용하는 자동차 지식 채널은 사실관계가 명확히 확인된 사건 위주로 시청하면 정보를 정확히 습득할 수 있습니다.</t>
   </si>
   <si>
     <t>미국</t>
   </si>
   <si>
-    <t>핫이슈</t>
-  </si>
-  <si>
-    <t>These Larry Bird Plays Would Go Viral Today</t>
-  </si>
-  <si>
-    <t>Sports Reaction' W SKSTR</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>이 영상은 보스턴 셀틱스의 전설 래리 버드의 플레이를 현대 농구의 관점에서 재해석합니다. 노룩 패스, 클러치 샷, 뛰어난 수비 판단력 등 신체 능력을 넘어선 그의 농구 지능과 창의성이 오늘날의 SNS 환경에서도 충분히 화제가 될 것임을 강조하며, 시대를 앞서간 그의 경기력을 상세히 분석합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 래리 버드가 현대 NBA에서도 여전히 슈퍼스타로 통할 수 있는 이유를 전술적인 관점에서 파악하면 농구를 보는 시야가 넓어집니다.</t>
-  </si>
-  <si>
-    <t>Pool Karen Calls Cops After Black Dad Refuses to Show ID</t>
-  </si>
-  <si>
-    <t>Willie D Live</t>
-  </si>
-  <si>
-    <t>2026-08-04</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>이 영상은 시카고의 한 수영장에서 인종차별적 이유로 흑인 아버지에게만 신분증 제시를 요구하며 경찰을 부른 '풀 카렌' 사건을 다룹니다. 진행자는 이 사건을 통해 일상 속 만연한 인종 프로파일링의 실태를 비판하고, 부당한 상황에서 자신의 권리를 지키는 태도의 중요성을 강조하며 사회적 메시지를 전달합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 갈등 상황을 강조한 클릭베이트 영상이므로, 실제 사건의 맥락과 양측의 주장을 객관적으로 검증하며 시청할 필요가 있습니다.</t>
-  </si>
-  <si>
     <t>Sajjala Comments On Borugadda Anil Incident | Sajjala Ramakrishna Reddy Press Meet On Borugadda Anil</t>
   </si>
   <si>
@@ -209,76 +170,85 @@
     <t>16:40</t>
   </si>
   <si>
-    <t>본 영상은 안드라프라데시주의 정치인 사잘라 라마크리슈나 레디가 보루가다 아닐 사건과 관련해 가진 기자회견 내용을 다룹니다. 그는 보루가다 아닐을 둘러싼 논란에 대해 공식적인 입장을 밝히고, 제기된 의혹들에 대해 해명하며 당의 견해를 전달하는 데 초점을 맞추고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 영상은 검색 엔진 최적화용 태그를 나열한 클릭베이트 성격이 강하므로, 실제 사건의 깊이 있는 분석보다는 정치적 대응의 요점 위주로 파악하는 것이 좋습니다.</t>
+    <t>본 영상은 YSRCP 고위 간부인 사잘라 라마크리슈나 레디가 보루가다 아닐과 관련된 논란에 대해 공식 입장을 밝히는 기자회견 내용을 담고 있습니다. 사잘라는 해당 사건에 대한 비판적 의견을 표명하며 당의 입장을 명확히 정리하고, 제기된 여러 의혹에 대해 해명하며 정치적 상황을 수습하려는 모습을 보입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 키워드를 반복 사용한 클릭베이트 성격의 정치 보도 영상이므로, 실제 공식 입장문과 함께 교차 검증하며 시청하는 것을 권장합니다.</t>
   </si>
   <si>
     <t>라이징스타</t>
   </si>
   <si>
-    <t>BTS 1 #viral</t>
-  </si>
-  <si>
-    <t>BTS  Film</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>5:24</t>
-  </si>
-  <si>
-    <t>본 영상은 그룹 BTS의 활동 모습이 담긴 짧은 쇼츠 영상입니다. 구체적인 대사나 자막은 없으나, BTS 멤버들의 매력적인 비주얼과 퍼포먼스 분위기를 시각적으로 강조하고 있습니다. 팬들을 위한 짧은 소장용 영상 콘텐츠로, 특정 메시지 전달보다는 멤버들의 아이코닉한 이미지를 감상하는 데 집중한 영상입니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 영상은 공식 뮤직비디오가 아닌 짧은 클립 형태의 바이럴성 영상이므로 단순 시청용으로 적합합니다.</t>
-  </si>
-  <si>
-    <t>[海外の反応]「日本は終わった国です」歴史的大勝利の翌朝、日本外務省"32文字の沈黙"に韓国エリート外交官が崩れ落ちた！</t>
-  </si>
-  <si>
-    <t>SMOKINGxKUSH</t>
-  </si>
-  <si>
-    <t>1:27:48</t>
-  </si>
-  <si>
-    <t>본 영상은 일본의 외교적 성과를 강조하며 한국과의 관계를 자극적으로 다루는 내셔널리즘 성향의 콘텐츠입니다. 구체적인 정보보다는 자극적인 제목과 문구를 사용하여 일본의 외교적 우위와 한국의 외교적 패배를 주장하는 전형적인 해외 반응 스타일의 선동형 영상을 표방하고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 해당 채널은 자극적인 제목과 클릭베이트를 통해 특정 국가 간 갈등을 조장하는 내용이 많으므로 사실관계 확인이 필요한 영상입니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White America PANICS as the Forbidden Truth About Black History Goes Viral... 😳🔥 #usa #usnews </t>
-  </si>
-  <si>
-    <t>Son Commentaries</t>
-  </si>
-  <si>
-    <t>36:46</t>
-  </si>
-  <si>
-    <t>본 영상은 미국 역사 속에서 제대로 다뤄지지 않았던 노예제, 인종 폭력, 원주민 학살 등 어두운 진실을 재조명하는 바이럴 콘텐츠를 다룹니다. 제작자는 주류 역사 서술에 의문을 제기하며 이러한 과거가 현대 미국 사회에 미치는 지속적인 영향에 대해 비판적이고 솔직한 시각으로 논평합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 제목과 썸네일을 사용한 클릭베이트 요소가 강하므로, 영상 내 주장의 객관적 근거를 교차 검증하며 시청하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>ドイツ人「熊本で日本人の底力を見た…！」熊本で生まれて初めて震度７の大地震を経験したドイツ人。直後、日本人たちの行動に衝撃を受けてしまう…【感動】</t>
-  </si>
-  <si>
-    <t>【海外の反応】海外ネキの衝撃JAPAN</t>
-  </si>
-  <si>
-    <t>10:33</t>
-  </si>
-  <si>
-    <t>본 영상은 구마모토 지진 당시 일본의 현장을 목격한 독일인의 시각을 다룹니다. 큰 재난 상황 속에서도 질서를 유지하고 서로 돕는 일본인들의 침착한 태도와 시민 의식에 깊은 감명을 받은 외국인의 반응을 2ch 스레드 형식으로 재구성하여 일본의 국민성을 칭찬하는 내용을 담고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 영상은 실제 사건을 바탕으로 하지만 인터넷 커뮤니티의 반응을 재구성한 자극적인 형식의 콘텐츠이므로 정보의 객관성보다는 일본 중심적인 감동 사례 위주임을 참고하시기 바랍니다.</t>
+    <t>TIKTOK MASHUP VIRAL AUGUST 2026 PHILIPPINES</t>
+  </si>
+  <si>
+    <t>Mashup</t>
+  </si>
+  <si>
+    <t>5:33</t>
+  </si>
+  <si>
+    <t>본 영상은 2026년 8월 필리핀 지역에서 유행한 틱톡 바이럴 콘텐츠를 모아 편집한 매시업 영상입니다. 다양한 틱톡 댄스 챌린지, 유머러스한 스키트, 그리고 최신 트렌드 영상을 하나로 엮어 시청자들에게 짧은 시간 동안 폭넓은 재미를 제공하는 것을 목적으로 합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 썸네일과 제목으로 클릭을 유도하는 콘텐츠이므로 유행 흐름을 파악하는 용도로 가볍게 시청하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>【大炎上】  BYD軽EVは本当に大丈夫か!? 返品の声と日本市場の現実</t>
+  </si>
+  <si>
+    <t>未来の日本車</t>
+  </si>
+  <si>
+    <t>31:06</t>
+  </si>
+  <si>
+    <t>본 영상은 일본 시장에 진출한 중국 BYD의 경형 전기차에 대한 논란과 품질 의구심을 다룹니다. 특히 일부 사용자들 사이에서 제기되는 반품 요구와 일본 내 실제 시장 반응을 분석하며, BYD의 가격 경쟁력이 가진 이면의 품질 문제와 일본 소비자들의 냉정한 평가를 심층적으로 짚어봅니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 제목에서 강조하는 '반품' 이슈는 파편적인 주장을 기반으로 한 자극적인 소재일 수 있으므로, 보도 내용과 실제 기술적 검증 데이터를 교차 확인하는 비판적 시각이 필요합니다.</t>
+  </si>
+  <si>
+    <t>Mayumi Tiktok Mashup</t>
+  </si>
+  <si>
+    <t>10:46</t>
+  </si>
+  <si>
+    <t>본 영상은 2026년 8월 필리핀 지역에서 큰 인기를 끈 틱톡의 바이럴 영상들을 하나로 편집한 매쉬업 콘텐츠입니다. 최신 트렌드 댄스부터 유머러스한 스킷까지 소셜 미디어상의 화제 영상을 집약하여 시청자들에게 빠른 호흡의 즐거움을 제공하며, 채널 구독과 알림 설정을 통해 지속적인 최신 콘텐츠 업데이트를 독려하고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️해당 영상은 높은 조회수를 노린 전형적인 클릭베이트형 매쉬업 콘텐츠이므로 정보성보다는 가벼운 오락 목적으로만 시청하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>August 07, 2026 : Up Breaking News | Today Up News | Uttar Pradesh Latest News | Cm Yogi News</t>
+  </si>
+  <si>
+    <t>UP दिशा News</t>
+  </si>
+  <si>
+    <t>17:32</t>
+  </si>
+  <si>
+    <t>본 영상은 2026년 8월 7일 기준 우타르프라데시 주의 주요 소식을 다루는 뉴스 브리핑입니다. CM 요기 아디티야나트 주총리의 최신 행보를 중심으로 우타르프라데시 주의 정치, 사회적 사안과 날씨 정보를 포함한 당일의 긴급 뉴스들을 요약하여 전달하고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 해당 영상은 조회수를 노린 전형적인 클릭베이트 형식을 띠고 있으므로, 정확한 현지 정보는 공신력 있는 언론사를 통해 확인하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>Viral OPM Hits 2026 🇵🇭 Trending Tagalog Love Songs 🎧 Spotify Playlist With Special Vibes</t>
+  </si>
+  <si>
+    <t>Calm Guitar</t>
+  </si>
+  <si>
+    <t>1:04:37</t>
+  </si>
+  <si>
+    <t>본 영상은 Calm Guitar 채널에서 제공하는 필리핀 대중음악(OPM) 및 타갈로그어 사랑 노래 모음집입니다. 공부, 업무, 운전, 휴식 등 일상 속 다양한 상황에서 편안한 분위기를 조성할 수 있도록 감성적인 곡들로 구성된 플레이리스트이며, 청취자에게 따뜻하고 안정적인 음악적 동반자가 되어줍니다.</t>
+  </si>
+  <si>
+    <t>음악과 함께 가사를 찾아보며 감상하면 타갈로그어 특유의 정서와 가사의 의미를 더 깊게 공감할 수 있습니다.</t>
   </si>
 </sst>
 </file>
@@ -665,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -750,16 +720,16 @@
         <v>24</v>
       </c>
       <c r="I2" s="3">
-        <v>31054</v>
+        <v>32230</v>
       </c>
       <c r="J2" s="3">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="K2" s="3">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L2" s="3">
-        <v>4523</v>
+        <v>4339</v>
       </c>
       <c r="M2" s="3">
         <v>25700</v>
@@ -806,22 +776,22 @@
         <v>33</v>
       </c>
       <c r="I3" s="3">
-        <v>151470</v>
+        <v>168275</v>
       </c>
       <c r="J3" s="3">
-        <v>1378</v>
+        <v>1472</v>
       </c>
       <c r="K3" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="L3" s="3">
-        <v>16655</v>
+        <v>16983</v>
       </c>
       <c r="M3" s="3">
         <v>144000</v>
       </c>
       <c r="N3" s="5">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="O3" s="4" t="s">
         <v>34</v>
@@ -862,22 +832,22 @@
         <v>39</v>
       </c>
       <c r="I4" s="3">
-        <v>118202</v>
+        <v>36304</v>
       </c>
       <c r="J4" s="3">
-        <v>1844</v>
+        <v>885</v>
       </c>
       <c r="K4" s="3">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="L4" s="3">
-        <v>13616</v>
+        <v>11333</v>
       </c>
       <c r="M4" s="3">
-        <v>189000</v>
-      </c>
-      <c r="N4" s="5">
-        <v>0.63</v>
+        <v>174000</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="O4" s="4" t="s">
         <v>40</v>
@@ -912,34 +882,34 @@
         <v>43</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="I5" s="3">
-        <v>23253</v>
+        <v>54821</v>
       </c>
       <c r="J5" s="3">
-        <v>700</v>
+        <v>1206</v>
       </c>
       <c r="K5" s="3">
-        <v>120</v>
+        <v>277</v>
       </c>
       <c r="L5" s="3">
-        <v>13027</v>
+        <v>8524</v>
       </c>
       <c r="M5" s="3">
-        <v>174000</v>
+        <v>31400</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>25</v>
       </c>
       <c r="O5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="P5" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>28</v>
@@ -953,166 +923,54 @@
         <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>38</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I6" s="3">
-        <v>21298</v>
+        <v>48580</v>
       </c>
       <c r="J6" s="3">
-        <v>876</v>
+        <v>550</v>
       </c>
       <c r="K6" s="3">
-        <v>126</v>
+        <v>168</v>
       </c>
       <c r="L6" s="3">
-        <v>4175</v>
+        <v>12724</v>
       </c>
       <c r="M6" s="3">
-        <v>1860</v>
+        <v>204000</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>25</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>28</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="2">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I7" s="3">
-        <v>130147</v>
-      </c>
-      <c r="J7" s="3">
-        <v>7802</v>
-      </c>
-      <c r="K7" s="3">
-        <v>1450</v>
-      </c>
-      <c r="L7" s="3">
-        <v>58434</v>
-      </c>
-      <c r="M7" s="3">
-        <v>1190000</v>
-      </c>
-      <c r="N7" s="5">
-        <v>0.11</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="2">
-        <v>2</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="I8" s="3">
-        <v>33475</v>
-      </c>
-      <c r="J8" s="3">
-        <v>410</v>
-      </c>
-      <c r="K8" s="3">
-        <v>131</v>
-      </c>
-      <c r="L8" s="3">
-        <v>14529</v>
-      </c>
-      <c r="M8" s="3">
-        <v>204000</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R8" s="2" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1123,8 +981,6 @@
     <hyperlink ref="Q4" r:id="rId3"/>
     <hyperlink ref="Q5" r:id="rId4"/>
     <hyperlink ref="Q6" r:id="rId5"/>
-    <hyperlink ref="Q7" r:id="rId6"/>
-    <hyperlink ref="Q8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1132,7 +988,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -1196,49 +1052,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="I2" s="3">
-        <v>190489</v>
+        <v>90905</v>
       </c>
       <c r="J2" s="3">
-        <v>380</v>
+        <v>194</v>
       </c>
       <c r="K2" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L2" s="3">
         <v>0</v>
       </c>
       <c r="M2" s="3">
-        <v>619</v>
+        <v>313</v>
       </c>
       <c r="N2" s="5">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>28</v>
@@ -1255,46 +1111,46 @@
         <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D3" s="2">
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="I3" s="3">
-        <v>51335</v>
+        <v>106466</v>
       </c>
       <c r="J3" s="3">
-        <v>702</v>
+        <v>2137</v>
       </c>
       <c r="K3" s="3">
-        <v>39</v>
+        <v>282</v>
       </c>
       <c r="L3" s="3">
         <v>0</v>
       </c>
       <c r="M3" s="3">
-        <v>2390</v>
+        <v>600</v>
       </c>
       <c r="N3" s="5">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>28</v>
@@ -1308,49 +1164,49 @@
         <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="I4" s="3">
-        <v>88475</v>
+        <v>86890</v>
       </c>
       <c r="J4" s="3">
-        <v>4462</v>
+        <v>150</v>
       </c>
       <c r="K4" s="3">
-        <v>1262</v>
+        <v>10</v>
       </c>
       <c r="L4" s="3">
         <v>0</v>
       </c>
       <c r="M4" s="3">
-        <v>8100</v>
+        <v>1050</v>
       </c>
       <c r="N4" s="5">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>28</v>
@@ -1364,54 +1220,110 @@
         <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D5" s="2">
         <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="I5" s="3">
-        <v>50879</v>
+        <v>114059</v>
       </c>
       <c r="J5" s="3">
-        <v>667</v>
+        <v>931</v>
       </c>
       <c r="K5" s="3">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="L5" s="3">
         <v>0</v>
       </c>
       <c r="M5" s="3">
-        <v>7270</v>
+        <v>2240</v>
       </c>
       <c r="N5" s="5">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>28</v>
       </c>
       <c r="R5" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I6" s="3">
+        <v>78254</v>
+      </c>
+      <c r="J6" s="3">
+        <v>375</v>
+      </c>
+      <c r="K6" s="3">
+        <v>10</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3">
+        <v>1780</v>
+      </c>
+      <c r="N6" s="5">
+        <v>44</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="R6" s="2" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1421,6 +1333,7 @@
     <hyperlink ref="Q3" r:id="rId2"/>
     <hyperlink ref="Q4" r:id="rId3"/>
     <hyperlink ref="Q5" r:id="rId4"/>
+    <hyperlink ref="Q6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
